--- a/registration_forms/033_ai_project_management_workshop_registration--registration_forms.xlsx
+++ b/registration_forms/033_ai_project_management_workshop_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,8 +957,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -986,12 +986,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'agile_/_scrum',_'value':_'agile'}</t>
+          <t>agile_/_scrum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Agile / Scrum', 'value': 'agile'}</t>
+          <t>Agile / Scrum</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'waterfall',_'value':_'waterfall'}</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Waterfall', 'value': 'waterfall'}</t>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'kanban',_'value':_'kanban'}</t>
+          <t>kanban</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Kanban', 'value': 'kanban'}</t>
+          <t>Kanban</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'lean',_'value':_'lean'}</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Lean', 'value': 'lean'}</t>
+          <t>Lean</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid', 'value': 'hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'jira_/_atlassian',_'value':_'jira'}</t>
+          <t>jira_/_atlassian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Jira / Atlassian', 'value': 'jira'}</t>
+          <t>Jira / Atlassian</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'asana',_'value':_'asana'}</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Asana', 'value': 'asana'}</t>
+          <t>Asana</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monday.com',_'value':_'monday'}</t>
+          <t>monday.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monday.com', 'value': 'monday'}</t>
+          <t>Monday.com</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'trello',_'value':_'trello'}</t>
+          <t>trello</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Trello', 'value': 'trello'}</t>
+          <t>Trello</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'microsoft_project',_'value':_'ms_project'}</t>
+          <t>microsoft_project</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Microsoft Project', 'value': 'ms_project'}</t>
+          <t>Microsoft Project</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'clickup',_'value':_'clickup'}</t>
+          <t>clickup</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'ClickUp', 'value': 'clickup'}</t>
+          <t>ClickUp</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'managing_data_quality_and_availability',_'value':_'data_issues'}</t>
+          <t>managing_data_quality_and_availability</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Managing Data Quality and Availability', 'value': 'data_issues'}</t>
+          <t>Managing Data Quality and Availability</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'uncertain_roi_and_timeline_estimates',_'value':_'roi_uncertainty'}</t>
+          <t>uncertain_roi_and_timeline_estimates</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Uncertain ROI and Timeline Estimates', 'value': 'roi_uncertainty'}</t>
+          <t>Uncertain ROI and Timeline Estimates</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bridging_the_gap_between_devs_and_stakeholders',_'value':_'communication'}</t>
+          <t>bridging_the_gap_between_devs_and_stakeholders</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Bridging the gap between Devs and Stakeholders', 'value': 'communication'}</t>
+          <t>Bridging the gap between Devs and Stakeholders</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ethical_and_compliance_oversight',_'value':_'ethics'}</t>
+          <t>ethical_and_compliance_oversight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Ethical and Compliance Oversight', 'value': 'ethics'}</t>
+          <t>Ethical and Compliance Oversight</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'keeping_up_with_rapid_tech_changes',_'value':_'tech_pace'}</t>
+          <t>keeping_up_with_rapid_tech_changes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Keeping up with Rapid Tech Changes', 'value': 'tech_pace'}</t>
+          <t>Keeping up with Rapid Tech Changes</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'ai_pm_essentials_(planning_&amp;_scoping)',_'value':_'essentials'}</t>
+          <t>ai_pm_essentials_(planning_&amp;_scoping)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'AI PM Essentials (Planning &amp; Scoping)', 'value': 'essentials'}</t>
+          <t>AI PM Essentials (Planning &amp; Scoping)</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_ai_pm_(lifecycle_&amp;_mlops_governance)',_'value':_'advanced'}</t>
+          <t>advanced_ai_pm_(lifecycle_&amp;_mlops_governance)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced AI PM (Lifecycle &amp; MLOps Governance)', 'value': 'advanced'}</t>
+          <t>Advanced AI PM (Lifecycle &amp; MLOps Governance)</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'october_05-06,_2026',_'value':_'oct_session'}</t>
+          <t>october_05-06,_2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'October 05-06, 2026', 'value': 'oct_session'}</t>
+          <t>October 05-06, 2026</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'november_12-13,_2026',_'value':_'nov_session'}</t>
+          <t>november_12-13,_2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'November 12-13, 2026', 'value': 'nov_session'}</t>
+          <t>November 12-13, 2026</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'virtual_(live_interactive)',_'value':_'virtual'}</t>
+          <t>virtual_(live_interactive)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Virtual (Live Interactive)', 'value': 'virtual'}</t>
+          <t>Virtual (Live Interactive)</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'in-person_(london_hub)',_'value':_'in_person'}</t>
+          <t>in-person_(london_hub)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person (London Hub)', 'value': 'in_person'}</t>
+          <t>In-Person (London Hub)</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'corporate_credit_card',_'value':_'credit_card'}</t>
+          <t>corporate_credit_card</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Corporate Credit Card', 'value': 'credit_card'}</t>
+          <t>Corporate Credit Card</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer_/_invoice',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer_/_invoice</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer / Invoice', 'value': 'bank_transfer'}</t>
+          <t>Bank Transfer / Invoice</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
